--- a/B34_seed彙整_11n_padded.xlsx
+++ b/B34_seed彙整_11n_padded.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="各seed" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="mean±SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="對齊報告" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="逐張長度誤差_跨seed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="長度vsGT_各seed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="對齊報告" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,50 +433,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>B3_中位數絕對誤差_原圖px</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>B3_bias_原圖px</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>B3_誤差SD_原圖px</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>B3_長度MAE_上顎_原圖px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>B3_長度MAE_下顎_原圖px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>B3_mask失敗張數</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>B3_建議複查張數</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>mask幾何_與Y相關r</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>mask幾何_px每mm_CV</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>冠寬比例尺_與Y相關r</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>冠寬比例尺_去bias_MAE_mm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>牙位基準_與Y相關r</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>牙位基準_去bias_MAE_mm</t>
         </is>
@@ -488,33 +505,42 @@
         <v>12.217</v>
       </c>
       <c r="C2" t="n">
+        <v>8.278</v>
+      </c>
+      <c r="D2" t="n">
         <v>-7.561</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>15.67</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>14.025</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>26</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>0.0548</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>0.4058</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>0.597</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>2.0163</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>0.4116</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>1.3209</v>
       </c>
     </row>
@@ -526,33 +552,42 @@
         <v>7.6</v>
       </c>
       <c r="C3" t="n">
+        <v>5.293</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.241</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>10.556</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>8.835000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.924</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>23</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>0.0617</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>0.4041</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>0.5577</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>2.0339</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>0.4116</v>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>1.3209</v>
       </c>
     </row>
@@ -564,33 +599,42 @@
         <v>11.845</v>
       </c>
       <c r="C4" t="n">
+        <v>7.559</v>
+      </c>
+      <c r="D4" t="n">
         <v>-4.234</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>15.782</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>13.323</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>25</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>0.0517</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>0.4083</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>0.5222</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>2.1068</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>0.4116</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>1.3209</v>
       </c>
     </row>
@@ -602,33 +646,42 @@
         <v>13.634</v>
       </c>
       <c r="C5" t="n">
+        <v>8.492000000000001</v>
+      </c>
+      <c r="D5" t="n">
         <v>-12.279</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>15.415</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.128</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>25</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>0.0502</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>0.409</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>0.5367</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>2.1276</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>0.4116</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>1.3209</v>
       </c>
     </row>
@@ -640,33 +693,42 @@
         <v>10.368</v>
       </c>
       <c r="C6" t="n">
+        <v>7.233</v>
+      </c>
+      <c r="D6" t="n">
         <v>-4.472</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>13.473</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>11.679</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.403</v>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>20</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>0.0522</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>0.4073</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>0.5654</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>2.0889</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>0.4116</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>1.3209</v>
       </c>
     </row>
@@ -681,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,14 +782,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B3_bias_原圖px</t>
+          <t>B3_中位數絕對誤差_原圖px</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-5.461</v>
+        <v>7.371</v>
       </c>
       <c r="C3" t="n">
-        <v>4.957206320096027</v>
+        <v>1.270015944781797</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
@@ -736,14 +798,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B3_誤差SD_原圖px</t>
+          <t>B3_bias_原圖px</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.1792</v>
+        <v>-5.461</v>
       </c>
       <c r="C4" t="n">
-        <v>2.232988513181382</v>
+        <v>4.957206320096027</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -752,14 +814,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B3_mask失敗張數</t>
+          <t>B3_誤差SD_原圖px</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>14.1792</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.232988513181382</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
@@ -768,14 +830,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B3_建議複查張數</t>
+          <t>B3_長度MAE_上顎_原圖px</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.8</v>
+        <v>12.7484</v>
       </c>
       <c r="C6" t="n">
-        <v>2.387467277262664</v>
+        <v>2.656365336319535</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -784,14 +846,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mask幾何_與Y相關r</t>
+          <t>B3_長度MAE_下顎_原圖px</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05412</v>
+        <v>5.015</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004550494478625371</v>
+        <v>1.243668364155011</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
@@ -800,14 +862,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mask幾何_px每mm_CV</t>
+          <t>B3_mask失敗張數</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4069</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001973575435599043</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -816,14 +878,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>冠寬比例尺_與Y相關r</t>
+          <t>B3_建議複查張數</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5558</v>
+        <v>23.8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02866609495553937</v>
+        <v>2.387467277262664</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -832,14 +894,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>冠寬比例尺_去bias_MAE_mm</t>
+          <t>mask幾何_與Y相關r</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0747</v>
+        <v>0.05412</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04771179099551803</v>
+        <v>0.004550494478625371</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -848,14 +910,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>牙位基準_與Y相關r</t>
+          <t>mask幾何_px每mm_CV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4116000000000001</v>
+        <v>0.4069</v>
       </c>
       <c r="C11" t="n">
-        <v>6.206335383118183e-17</v>
+        <v>0.001973575435599043</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -864,16 +926,64 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>冠寬比例尺_與Y相關r</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5558</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.02866609495553937</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>冠寬比例尺_去bias_MAE_mm</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.0747</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.04771179099551803</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>牙位基準_與Y相關r</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4116000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6.206335383118183e-17</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>牙位基準_去bias_MAE_mm</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B15" t="n">
         <v>1.3209</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D15" t="n">
         <v>5</v>
       </c>
     </row>
@@ -888,6 +998,5940 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:T68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>圖片檔名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>牙位</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>上下顎</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>GT長度_原圖px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>跨seed平均預測_原圖px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>跨seed預測SD_原圖px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>跨seed平均誤差_預測減GT_原圖px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>跨seed_MAE_原圖px</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>跨seed相對誤差%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>有效seed數</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>預測_seed0</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>絕對誤差_seed0</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>預測_seed1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>絕對誤差_seed1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>預測_seed2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>絕對誤差_seed2</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>預測_seed3</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>絕對誤差_seed3</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>預測_seed4</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>絕對誤差_seed4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>009_d1_jpg.rf.a4e9643443ee2e940ab17d8bc2f79ed4.jpg</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1328.0817</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1290.1339</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17.7074</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-37.9478</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37.9478</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.8573</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1283.9973</v>
+      </c>
+      <c r="L2" t="n">
+        <v>44.0844</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1310.8114</v>
+      </c>
+      <c r="N2" t="n">
+        <v>17.2703</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1295.665</v>
+      </c>
+      <c r="P2" t="n">
+        <v>32.4167</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1263.4103</v>
+      </c>
+      <c r="R2" t="n">
+        <v>64.67140000000001</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1296.7856</v>
+      </c>
+      <c r="T2" t="n">
+        <v>31.2961</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>017_d0_jpg.rf.e371f94baddb2eaf7462ec73ce042fb3.jpg</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1498.2369</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1465.7876</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.8276</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-32.4493</v>
+      </c>
+      <c r="H3" t="n">
+        <v>32.4493</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.1658</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1452.2846</v>
+      </c>
+      <c r="L3" t="n">
+        <v>45.9523</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1475.859</v>
+      </c>
+      <c r="N3" t="n">
+        <v>22.3779</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1468.0412</v>
+      </c>
+      <c r="P3" t="n">
+        <v>30.1957</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1459.4198</v>
+      </c>
+      <c r="R3" t="n">
+        <v>38.8171</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1473.3333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>24.9036</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>011_d0_jpg.rf.8592f84486d3e21026a0de8bd8475f37.jpg</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>777.3482</v>
+      </c>
+      <c r="E4" t="n">
+        <v>745.7762</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17.7174</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-31.572</v>
+      </c>
+      <c r="H4" t="n">
+        <v>31.572</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.0615</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>750.1117</v>
+      </c>
+      <c r="L4" t="n">
+        <v>27.2365</v>
+      </c>
+      <c r="M4" t="n">
+        <v>767.7139</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.6343</v>
+      </c>
+      <c r="O4" t="n">
+        <v>745.028</v>
+      </c>
+      <c r="P4" t="n">
+        <v>32.3202</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>718.3638</v>
+      </c>
+      <c r="R4" t="n">
+        <v>58.9844</v>
+      </c>
+      <c r="S4" t="n">
+        <v>747.6636</v>
+      </c>
+      <c r="T4" t="n">
+        <v>29.6846</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>032_d0_jpg.rf.9285b7976f1da306fcfec57b8ac03392.jpg</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1361.5634</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1330.1853</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.5179</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-31.3781</v>
+      </c>
+      <c r="H5" t="n">
+        <v>31.3781</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.3046</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1312.2254</v>
+      </c>
+      <c r="L5" t="n">
+        <v>49.338</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1347.4606</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14.1028</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1338.6167</v>
+      </c>
+      <c r="P5" t="n">
+        <v>22.9467</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1324.2094</v>
+      </c>
+      <c r="R5" t="n">
+        <v>37.354</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1328.4146</v>
+      </c>
+      <c r="T5" t="n">
+        <v>33.1488</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>039_d1_jpg.rf.d49148703ce141d56d8246b6549a4760.jpg</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>761.741</v>
+      </c>
+      <c r="E6" t="n">
+        <v>734.3472</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.6682</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-27.3938</v>
+      </c>
+      <c r="H6" t="n">
+        <v>27.3938</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.5962</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>724.9962</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36.7448</v>
+      </c>
+      <c r="M6" t="n">
+        <v>756.4476</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.2934</v>
+      </c>
+      <c r="O6" t="n">
+        <v>726.808</v>
+      </c>
+      <c r="P6" t="n">
+        <v>34.933</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>724.6361000000001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>37.1049</v>
+      </c>
+      <c r="S6" t="n">
+        <v>738.8483</v>
+      </c>
+      <c r="T6" t="n">
+        <v>22.8927</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>069_d0_jpg.rf.e7743bd9b6bf261cd082bb4e0ea61007.jpg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>729.8456</v>
+      </c>
+      <c r="E7" t="n">
+        <v>702.6698</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18.7916</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-27.1758</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27.1758</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.7235</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>672.9195</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.9261</v>
+      </c>
+      <c r="M7" t="n">
+        <v>722.7687</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.0769</v>
+      </c>
+      <c r="O7" t="n">
+        <v>698.0498</v>
+      </c>
+      <c r="P7" t="n">
+        <v>31.7958</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>709.4403</v>
+      </c>
+      <c r="R7" t="n">
+        <v>20.4053</v>
+      </c>
+      <c r="S7" t="n">
+        <v>710.1704999999999</v>
+      </c>
+      <c r="T7" t="n">
+        <v>19.6751</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>034_d1_jpg.rf.c71a61069d50d94065010b64a9ffd1a5.jpg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1363.4817</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1388.3843</v>
+      </c>
+      <c r="F8" t="n">
+        <v>26.0407</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24.9026</v>
+      </c>
+      <c r="H8" t="n">
+        <v>26.6704</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9561</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1359.0623</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.4194</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1385.5736</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22.0919</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1425.1243</v>
+      </c>
+      <c r="P8" t="n">
+        <v>61.6426</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1370.5188</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7.0371</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1401.6427</v>
+      </c>
+      <c r="T8" t="n">
+        <v>38.161</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>021_d1_jpg.rf.ce2222b68f762d4951ed21a7e32abfa1.jpg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>646.6065</v>
+      </c>
+      <c r="E9" t="n">
+        <v>621.1558</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.8475</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-25.4507</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25.4507</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.936</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>622.2263</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.3802</v>
+      </c>
+      <c r="M9" t="n">
+        <v>633.8854</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12.7211</v>
+      </c>
+      <c r="O9" t="n">
+        <v>619.3691</v>
+      </c>
+      <c r="P9" t="n">
+        <v>27.2374</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>613.1756</v>
+      </c>
+      <c r="R9" t="n">
+        <v>33.4309</v>
+      </c>
+      <c r="S9" t="n">
+        <v>617.1226</v>
+      </c>
+      <c r="T9" t="n">
+        <v>29.4839</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>066_d1_jpg.rf.cca8412d959b332e5836a79cb1f63bb9.jpg</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>701.1987</v>
+      </c>
+      <c r="E10" t="n">
+        <v>677.7583</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14.0633</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-23.4404</v>
+      </c>
+      <c r="H10" t="n">
+        <v>23.4404</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3429</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>683.3661</v>
+      </c>
+      <c r="L10" t="n">
+        <v>17.8326</v>
+      </c>
+      <c r="M10" t="n">
+        <v>697.2397</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.959</v>
+      </c>
+      <c r="O10" t="n">
+        <v>675.0444</v>
+      </c>
+      <c r="P10" t="n">
+        <v>26.1543</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>658.7461</v>
+      </c>
+      <c r="R10" t="n">
+        <v>42.4526</v>
+      </c>
+      <c r="S10" t="n">
+        <v>674.3954</v>
+      </c>
+      <c r="T10" t="n">
+        <v>26.8033</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>047_d0_jpg.rf.7cdd34b48873ec944be1cf54e2bbe7de.jpg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>604.1849</v>
+      </c>
+      <c r="E11" t="n">
+        <v>582.9991</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.3012</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-21.1858</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21.1858</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.5065</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>584.8191</v>
+      </c>
+      <c r="L11" t="n">
+        <v>19.3658</v>
+      </c>
+      <c r="M11" t="n">
+        <v>585.5338</v>
+      </c>
+      <c r="N11" t="n">
+        <v>18.6511</v>
+      </c>
+      <c r="O11" t="n">
+        <v>582.9046</v>
+      </c>
+      <c r="P11" t="n">
+        <v>21.2803</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>581.9559</v>
+      </c>
+      <c r="R11" t="n">
+        <v>22.229</v>
+      </c>
+      <c r="S11" t="n">
+        <v>579.7822</v>
+      </c>
+      <c r="T11" t="n">
+        <v>24.4027</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>065_d0_jpg.rf.ee2a42597e7bd3f73156286c58ff062a.jpg</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>706.3221</v>
+      </c>
+      <c r="E12" t="n">
+        <v>687.1061999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11.409</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-19.2159</v>
+      </c>
+      <c r="H12" t="n">
+        <v>19.2159</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.7206</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>699.4342</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.8879</v>
+      </c>
+      <c r="M12" t="n">
+        <v>693.9326</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.3895</v>
+      </c>
+      <c r="O12" t="n">
+        <v>680.1435</v>
+      </c>
+      <c r="P12" t="n">
+        <v>26.1786</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>671.0282999999999</v>
+      </c>
+      <c r="R12" t="n">
+        <v>35.2938</v>
+      </c>
+      <c r="S12" t="n">
+        <v>690.9922</v>
+      </c>
+      <c r="T12" t="n">
+        <v>15.3299</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>063_d1_jpg.rf.3d9a28c55c36d0806810a87e5ea9470f.jpg</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>702.633</v>
+      </c>
+      <c r="E13" t="n">
+        <v>684.8642</v>
+      </c>
+      <c r="F13" t="n">
+        <v>17.1771</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-17.7688</v>
+      </c>
+      <c r="H13" t="n">
+        <v>17.7688</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.5289</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>695.502</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7.131</v>
+      </c>
+      <c r="M13" t="n">
+        <v>686.5624</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.0706</v>
+      </c>
+      <c r="O13" t="n">
+        <v>689.6813</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12.9517</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>655.1471</v>
+      </c>
+      <c r="R13" t="n">
+        <v>47.4859</v>
+      </c>
+      <c r="S13" t="n">
+        <v>697.428</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5.205</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>031_d1_jpg.rf.0a64e6a881d6244f0916844a19eec968.jpg</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1379.8469</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1362.2222</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.4977</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-17.6247</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17.6247</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.2773</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1356.9842</v>
+      </c>
+      <c r="L14" t="n">
+        <v>22.8627</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1359.1185</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20.7284</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1366.6507</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13.1962</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1353.5838</v>
+      </c>
+      <c r="R14" t="n">
+        <v>26.2631</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1374.7736</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5.0733</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>048_d0_jpg.rf.b9d97351b8bbb80a941065b51ab298c2.jpg</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1446.249</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1457.5886</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18.4215</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11.3396</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16.9821</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1742</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1457.3396</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11.0906</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1482.2127</v>
+      </c>
+      <c r="N15" t="n">
+        <v>35.9637</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1465.2978</v>
+      </c>
+      <c r="P15" t="n">
+        <v>19.0488</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1432.1427</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14.1063</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1450.9502</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.7012</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>030_d1_jpg.rf.642032a0ccf11c21478fc98e431d62c2.jpg</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>702.6124</v>
+      </c>
+      <c r="E16" t="n">
+        <v>686.3732</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.9799</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-16.2392</v>
+      </c>
+      <c r="H16" t="n">
+        <v>16.2392</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3113</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>683.4626</v>
+      </c>
+      <c r="L16" t="n">
+        <v>19.1498</v>
+      </c>
+      <c r="M16" t="n">
+        <v>690.0057</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12.6067</v>
+      </c>
+      <c r="O16" t="n">
+        <v>685.6106</v>
+      </c>
+      <c r="P16" t="n">
+        <v>17.0018</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>683.8176</v>
+      </c>
+      <c r="R16" t="n">
+        <v>18.7948</v>
+      </c>
+      <c r="S16" t="n">
+        <v>688.9693</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13.6431</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>022_d1_jpg.rf.f1be5fe64a13290e324eac2bae09a30c.jpg</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>692.252</v>
+      </c>
+      <c r="E17" t="n">
+        <v>677.4141</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.587199999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-14.8379</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14.8379</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1434</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>671.4820999999999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20.7699</v>
+      </c>
+      <c r="M17" t="n">
+        <v>690.6223</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.6297</v>
+      </c>
+      <c r="O17" t="n">
+        <v>681.0434</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11.2086</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>674.4791</v>
+      </c>
+      <c r="R17" t="n">
+        <v>17.7729</v>
+      </c>
+      <c r="S17" t="n">
+        <v>669.4437</v>
+      </c>
+      <c r="T17" t="n">
+        <v>22.8083</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>059_d1_jpg.rf.3f42e0602c43c121b117dcecca57b59d.jpg</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>696.0694</v>
+      </c>
+      <c r="E18" t="n">
+        <v>705.7641</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17.0552</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9.694699999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>14.3165</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.0568</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>727.9077</v>
+      </c>
+      <c r="L18" t="n">
+        <v>31.8383</v>
+      </c>
+      <c r="M18" t="n">
+        <v>697.8854</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="O18" t="n">
+        <v>717.4779</v>
+      </c>
+      <c r="P18" t="n">
+        <v>21.4085</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>684.5148</v>
+      </c>
+      <c r="R18" t="n">
+        <v>11.5546</v>
+      </c>
+      <c r="S18" t="n">
+        <v>701.0347</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.9653</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>013_d1_jpg.rf.b7990f89d66aa887a430c51d7385ddcd.jpg</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>692.9842</v>
+      </c>
+      <c r="E19" t="n">
+        <v>679.8092</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.5031</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-13.175</v>
+      </c>
+      <c r="H19" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.9012</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>674.4598999999999</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18.5243</v>
+      </c>
+      <c r="M19" t="n">
+        <v>690.9687</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.0155</v>
+      </c>
+      <c r="O19" t="n">
+        <v>678.6433</v>
+      </c>
+      <c r="P19" t="n">
+        <v>14.3409</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>672.0146</v>
+      </c>
+      <c r="R19" t="n">
+        <v>20.9696</v>
+      </c>
+      <c r="S19" t="n">
+        <v>682.9595</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10.0247</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>049_d0_jpg.rf.a92e6c133f098bc8b880cd0c95917303.jpg</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1414.7345</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1402.9685</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.643599999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-11.766</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12.5023</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8837</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1394.6959</v>
+      </c>
+      <c r="L20" t="n">
+        <v>20.0386</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1416.5751</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.8406</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1408.4325</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6.302</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1393.6792</v>
+      </c>
+      <c r="R20" t="n">
+        <v>21.0553</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1401.4597</v>
+      </c>
+      <c r="T20" t="n">
+        <v>13.2748</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>003_d1_jpg.rf.38cc6ea2963bec79f589d69fb3c38567.jpg</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>21</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>765.3126999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>759.9795</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13.7299</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-5.3332</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11.7558</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.5361</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>773.5911</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8.2784</v>
+      </c>
+      <c r="M21" t="n">
+        <v>773.0906</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7.7779</v>
+      </c>
+      <c r="O21" t="n">
+        <v>755.0650000000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10.2477</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>740.8621000000001</v>
+      </c>
+      <c r="R21" t="n">
+        <v>24.4506</v>
+      </c>
+      <c r="S21" t="n">
+        <v>757.2885</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8.0242</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>050_d1_jpg.rf.84fe073fb9b1dc338920f1a858bf5e87.jpg</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>22</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1418.9283</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1407.19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12.0538</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-11.7383</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11.7476</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1393.5521</v>
+      </c>
+      <c r="L22" t="n">
+        <v>25.3762</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1413.2711</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.6572</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1415.3598</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.5685</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1418.9515</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1394.8156</v>
+      </c>
+      <c r="T22" t="n">
+        <v>24.1127</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>051_d0_jpg.rf.37687ccc93b1c959bc854c565f03d537.jpg</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1340.9003</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1329.3987</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.0414</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-11.5016</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11.5016</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8577</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1328.9452</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11.9551</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1335.4399</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.4604</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1333.634</v>
+      </c>
+      <c r="P23" t="n">
+        <v>7.2663</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1319.8445</v>
+      </c>
+      <c r="R23" t="n">
+        <v>21.0558</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1329.1301</v>
+      </c>
+      <c r="T23" t="n">
+        <v>11.7702</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>038_d1_jpg.rf.b3c9c20efafeb14a18e816c6ca8d7855.jpg</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>601.1339</v>
+      </c>
+      <c r="E24" t="n">
+        <v>601.9721</v>
+      </c>
+      <c r="F24" t="n">
+        <v>16.9048</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11.3579</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.8894</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>590.0445999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>11.0893</v>
+      </c>
+      <c r="M24" t="n">
+        <v>630.807</v>
+      </c>
+      <c r="N24" t="n">
+        <v>29.6731</v>
+      </c>
+      <c r="O24" t="n">
+        <v>601.951</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.8171</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>589.8686</v>
+      </c>
+      <c r="R24" t="n">
+        <v>11.2653</v>
+      </c>
+      <c r="S24" t="n">
+        <v>597.1891000000001</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.9448</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>006_d1_jpg.rf.3c7d07d05aae59d1f393853f31eb78a9.jpg</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>721.6917999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>712.9263</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13.5513</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-8.765499999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11.2449</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.5581</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>720.9897999999999</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="M25" t="n">
+        <v>727.8902</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6.1984</v>
+      </c>
+      <c r="O25" t="n">
+        <v>691.866</v>
+      </c>
+      <c r="P25" t="n">
+        <v>29.8258</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>711.674</v>
+      </c>
+      <c r="R25" t="n">
+        <v>10.0178</v>
+      </c>
+      <c r="S25" t="n">
+        <v>712.2113000000001</v>
+      </c>
+      <c r="T25" t="n">
+        <v>9.480499999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>070_d1_jpg.rf.dc10b95de92898fa67c004505cf51be2.jpg</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>647.4109999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>636.205</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.9645</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-11.206</v>
+      </c>
+      <c r="H26" t="n">
+        <v>11.206</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.7309</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>637.3348</v>
+      </c>
+      <c r="L26" t="n">
+        <v>10.0762</v>
+      </c>
+      <c r="M26" t="n">
+        <v>644.7212</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.6898</v>
+      </c>
+      <c r="O26" t="n">
+        <v>634.0834</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13.3276</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>625.832</v>
+      </c>
+      <c r="R26" t="n">
+        <v>21.579</v>
+      </c>
+      <c r="S26" t="n">
+        <v>639.0538</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8.357200000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>061_d1_jpg.rf.db8df0c1f429b3e2e71267f1fbffc989.jpg</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1111.8819</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1106.9352</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12.4019</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-4.9467</v>
+      </c>
+      <c r="H27" t="n">
+        <v>11.1102</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1120.8548</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.972899999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1118.3177</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6.4358</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1094.7168</v>
+      </c>
+      <c r="P27" t="n">
+        <v>17.1651</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1105.7334</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6.1485</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1095.0534</v>
+      </c>
+      <c r="T27" t="n">
+        <v>16.8285</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>008_d1_jpg.rf.fbef341d23507d0e4aca06499a411bb3.jpg</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>383.8256</v>
+      </c>
+      <c r="E28" t="n">
+        <v>394.1475</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7.4591</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10.3219</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10.3219</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.6892</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>400.0778</v>
+      </c>
+      <c r="L28" t="n">
+        <v>16.2522</v>
+      </c>
+      <c r="M28" t="n">
+        <v>392.1075</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8.2819</v>
+      </c>
+      <c r="O28" t="n">
+        <v>403.2632</v>
+      </c>
+      <c r="P28" t="n">
+        <v>19.4376</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>390.4331</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6.6075</v>
+      </c>
+      <c r="S28" t="n">
+        <v>384.8561</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.0305</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>071_d2_jpg.rf.0959cd07ae695e4405ee3ab991b172da.jpg</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>31</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>898.8659</v>
+      </c>
+      <c r="E29" t="n">
+        <v>890.2154</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8.096</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-8.650499999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>9.7553</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.0853</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>879.038</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.8279</v>
+      </c>
+      <c r="M29" t="n">
+        <v>901.6277</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.7618</v>
+      </c>
+      <c r="O29" t="n">
+        <v>888.3499</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10.516</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>889.9828</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8.883100000000001</v>
+      </c>
+      <c r="S29" t="n">
+        <v>892.0784</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6.7875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>057_d2_jpg.rf.cdb9bd6640c5fb65eee49172b52cbf93.jpg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>42</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1123.5509</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1133.2033</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7.6207</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.6524</v>
+      </c>
+      <c r="H30" t="n">
+        <v>9.6524</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1127.4478</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3.8969</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1131.5946</v>
+      </c>
+      <c r="N30" t="n">
+        <v>8.043699999999999</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1133.0387</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9.4878</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1127.7966</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4.2457</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1146.1387</v>
+      </c>
+      <c r="T30" t="n">
+        <v>22.5878</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>042_d2_jpg.rf.b762e168ff32523cefa4b66b23ff4fa2.jpg</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>22</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1177.23</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1181.6275</v>
+      </c>
+      <c r="F31" t="n">
+        <v>11.1996</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.3975</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.3378</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7932</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1193.8899</v>
+      </c>
+      <c r="L31" t="n">
+        <v>16.6599</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1179.4712</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.2412</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1192.6673</v>
+      </c>
+      <c r="P31" t="n">
+        <v>15.4373</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1171.8478</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5.3822</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1170.2615</v>
+      </c>
+      <c r="T31" t="n">
+        <v>6.9685</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>028_d1_jpg.rf.c32bbe4c003dc55f0e7db7b213e120d5.jpg</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>21</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>677.5697</v>
+      </c>
+      <c r="E32" t="n">
+        <v>686.0533</v>
+      </c>
+      <c r="F32" t="n">
+        <v>11.0753</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8.483599999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.8117</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.3005</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>684.712</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.1423</v>
+      </c>
+      <c r="M32" t="n">
+        <v>684.6488000000001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7.0791</v>
+      </c>
+      <c r="O32" t="n">
+        <v>679.2773</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.7076</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>676.7494</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.8203</v>
+      </c>
+      <c r="S32" t="n">
+        <v>704.8789</v>
+      </c>
+      <c r="T32" t="n">
+        <v>27.3092</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>002_d0_jpg.rf.239b012acf3a5d81cc23f63768811eab.jpg</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>614.2729</v>
+      </c>
+      <c r="E33" t="n">
+        <v>613.5937</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10.1882</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.6792</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.3626</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>605.6229</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="M33" t="n">
+        <v>629.0265000000001</v>
+      </c>
+      <c r="N33" t="n">
+        <v>14.7536</v>
+      </c>
+      <c r="O33" t="n">
+        <v>609.2073</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5.0656</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>605.3653</v>
+      </c>
+      <c r="R33" t="n">
+        <v>8.9076</v>
+      </c>
+      <c r="S33" t="n">
+        <v>618.7463</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4.4734</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>012_d1_jpg.rf.8f5edc0c4d896e0ac72c42fad4b4ae7e.jpg</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>22</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>665.6044000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>671.5237</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.3398</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.9193</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8.299899999999999</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>675.261</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.656599999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>678.6898</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13.0854</v>
+      </c>
+      <c r="O34" t="n">
+        <v>674.1031</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8.498699999999999</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>669.9116</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4.3072</v>
+      </c>
+      <c r="S34" t="n">
+        <v>659.6528</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5.9516</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>019_d1_jpg.rf.b5bbd4289ae38c62eccbabb5ba23cee6.jpg</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>763.8963</v>
+      </c>
+      <c r="E35" t="n">
+        <v>756.2205</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.3601</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-7.6758</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7.6758</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>750.3228</v>
+      </c>
+      <c r="L35" t="n">
+        <v>13.5735</v>
+      </c>
+      <c r="M35" t="n">
+        <v>763.8814</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="O35" t="n">
+        <v>758.9358999999999</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4.9604</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>755.404</v>
+      </c>
+      <c r="R35" t="n">
+        <v>8.4923</v>
+      </c>
+      <c r="S35" t="n">
+        <v>752.5583</v>
+      </c>
+      <c r="T35" t="n">
+        <v>11.338</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>041_d1_jpg.rf.cb07a3b2089be3295cec77cb809df396.jpg</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>21</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>702.189</v>
+      </c>
+      <c r="E36" t="n">
+        <v>695.8244</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8.9724</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-6.3646</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.6564</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.0904</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>692.8149</v>
+      </c>
+      <c r="L36" t="n">
+        <v>9.3741</v>
+      </c>
+      <c r="M36" t="n">
+        <v>705.4185</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.2295</v>
+      </c>
+      <c r="O36" t="n">
+        <v>700.0459</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.1431</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>681.9153</v>
+      </c>
+      <c r="R36" t="n">
+        <v>20.2737</v>
+      </c>
+      <c r="S36" t="n">
+        <v>698.9272</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.2618</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>027_d0_jpg.rf.172e9a9162be8b33b29886a7a7c2044f.jpg</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>11</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>650.6983</v>
+      </c>
+      <c r="E37" t="n">
+        <v>644.7504</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.1606</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-5.9479</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7.5875</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>641.4787</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9.2196</v>
+      </c>
+      <c r="M37" t="n">
+        <v>654.7971</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4.0988</v>
+      </c>
+      <c r="O37" t="n">
+        <v>643.0644</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7.6339</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>638.7143</v>
+      </c>
+      <c r="R37" t="n">
+        <v>11.984</v>
+      </c>
+      <c r="S37" t="n">
+        <v>645.6973</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5.001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>023_d1_jpg.rf.19149aa200ed2ab6d2f9f95936683869.jpg</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>21</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>591.2734</v>
+      </c>
+      <c r="E38" t="n">
+        <v>584.7868999999999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.8433</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-6.4865</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7.5062</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.2695</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>582.9601</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8.3133</v>
+      </c>
+      <c r="M38" t="n">
+        <v>593.8226</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.5492</v>
+      </c>
+      <c r="O38" t="n">
+        <v>585.4384</v>
+      </c>
+      <c r="P38" t="n">
+        <v>5.835</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>577.6724</v>
+      </c>
+      <c r="R38" t="n">
+        <v>13.601</v>
+      </c>
+      <c r="S38" t="n">
+        <v>584.0409</v>
+      </c>
+      <c r="T38" t="n">
+        <v>7.2325</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>037_d0_jpg.rf.26d3c419d8aa463d4ccb6f397ffd8a0d.jpg</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>21</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>615.7518</v>
+      </c>
+      <c r="E39" t="n">
+        <v>622.7236</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.1716</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.9718</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.9718</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.1322</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>623.0913</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.3395</v>
+      </c>
+      <c r="M39" t="n">
+        <v>626.0481</v>
+      </c>
+      <c r="N39" t="n">
+        <v>10.2963</v>
+      </c>
+      <c r="O39" t="n">
+        <v>622.6805000000001</v>
+      </c>
+      <c r="P39" t="n">
+        <v>6.9287</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>620.1864</v>
+      </c>
+      <c r="R39" t="n">
+        <v>4.4346</v>
+      </c>
+      <c r="S39" t="n">
+        <v>621.6117</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5.8599</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>024_d2_jpg.rf.dfde607ee1a1abd88070f4a4e9c873a7.jpg</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>22</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>574.4554000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>581.1653</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.7163</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.7099</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.7099</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>577.6952</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.2398</v>
+      </c>
+      <c r="M40" t="n">
+        <v>586.3052</v>
+      </c>
+      <c r="N40" t="n">
+        <v>11.8498</v>
+      </c>
+      <c r="O40" t="n">
+        <v>581.173</v>
+      </c>
+      <c r="P40" t="n">
+        <v>6.7176</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>577.5537</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3.0983</v>
+      </c>
+      <c r="S40" t="n">
+        <v>583.0995</v>
+      </c>
+      <c r="T40" t="n">
+        <v>8.6441</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>054_d3_jpg.rf.873773ad3ada175d0933d8f47c5af6c8.jpg</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>32</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1236.8036</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1230.1573</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.1448</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-6.6463</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6.6463</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1232.3472</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4.4564</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1234.5901</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.2135</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1231.6511</v>
+      </c>
+      <c r="P41" t="n">
+        <v>5.1525</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1230.9086</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1221.2897</v>
+      </c>
+      <c r="T41" t="n">
+        <v>15.5139</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>056_d1_jpg.rf.9429abcc45818b6e31b5dd0c7d043dfd.jpg</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1190.7387</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1186.2498</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.3731</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-4.4889</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6.6372</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1179.067</v>
+      </c>
+      <c r="L42" t="n">
+        <v>11.6717</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1184.3447</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6.394</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1188.07</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.6687</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1183.6579</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7.0808</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1196.1094</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5.3707</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>043_d1_jpg.rf.ff8a6dfd8d13cd19c47af53d9384c375.jpg</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>668.7536</v>
+      </c>
+      <c r="E43" t="n">
+        <v>673.0299</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8.6348</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.2763</v>
+      </c>
+      <c r="H43" t="n">
+        <v>6.4325</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>666.3632</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.3904</v>
+      </c>
+      <c r="M43" t="n">
+        <v>687.1897</v>
+      </c>
+      <c r="N43" t="n">
+        <v>18.4361</v>
+      </c>
+      <c r="O43" t="n">
+        <v>673.3241</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4.5705</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>665.7536</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>672.519</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.7654</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>020_d0_jpg.rf.ac00bbc8dce23d8bb488146d95350cfe.jpg</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>11</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>340.6128</v>
+      </c>
+      <c r="E44" t="n">
+        <v>347.018</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.2402</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.4052</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.4052</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.8805</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>345.2292</v>
+      </c>
+      <c r="L44" t="n">
+        <v>4.6164</v>
+      </c>
+      <c r="M44" t="n">
+        <v>348.1417</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7.5289</v>
+      </c>
+      <c r="O44" t="n">
+        <v>347.6124</v>
+      </c>
+      <c r="P44" t="n">
+        <v>6.9996</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>344.2916</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3.6788</v>
+      </c>
+      <c r="S44" t="n">
+        <v>349.8153</v>
+      </c>
+      <c r="T44" t="n">
+        <v>9.202500000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>060_jpg.rf.4a64dc5e1c74ac81bc312481b7e581e5.jpg</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>41</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>644.2548</v>
+      </c>
+      <c r="E45" t="n">
+        <v>646.0481</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8.407299999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.7933</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6.3802</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9903</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>646.0248</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M45" t="n">
+        <v>647.321</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.0662</v>
+      </c>
+      <c r="O45" t="n">
+        <v>656.1237</v>
+      </c>
+      <c r="P45" t="n">
+        <v>11.8689</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>632.7874</v>
+      </c>
+      <c r="R45" t="n">
+        <v>11.4674</v>
+      </c>
+      <c r="S45" t="n">
+        <v>647.9835</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.7287</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>064_d2_jpg.rf.7b174bc08e6f9220d59234147d56740a.jpg</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>22</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>645.8946999999999</v>
+      </c>
+      <c r="E46" t="n">
+        <v>647.857</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8.7598</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.9623</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6.0144</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9312</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>639.4633</v>
+      </c>
+      <c r="L46" t="n">
+        <v>6.4314</v>
+      </c>
+      <c r="M46" t="n">
+        <v>662.1129</v>
+      </c>
+      <c r="N46" t="n">
+        <v>16.2182</v>
+      </c>
+      <c r="O46" t="n">
+        <v>646.9873</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.0926</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>642.1959000000001</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3.6988</v>
+      </c>
+      <c r="S46" t="n">
+        <v>648.5258</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.6311</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>026_d1_jpg.rf.cbebc4e773617f19901fea82d27a7481.jpg</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>21</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>685.4338</v>
+      </c>
+      <c r="E47" t="n">
+        <v>691.2857</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.5585</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.8519</v>
+      </c>
+      <c r="H47" t="n">
+        <v>5.8519</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>689.2102</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.7764</v>
+      </c>
+      <c r="M47" t="n">
+        <v>691.7609</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6.3271</v>
+      </c>
+      <c r="O47" t="n">
+        <v>692.9924</v>
+      </c>
+      <c r="P47" t="n">
+        <v>7.5586</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>688.1723</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.7385</v>
+      </c>
+      <c r="S47" t="n">
+        <v>694.2929</v>
+      </c>
+      <c r="T47" t="n">
+        <v>8.8591</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>007_d1_jpg.rf.dd647087a302f451c265723a4c79a4f4.jpg</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>767.3638999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>763.3334</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.8126</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-4.0305</v>
+      </c>
+      <c r="H48" t="n">
+        <v>5.783</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>758.0549</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9.308999999999999</v>
+      </c>
+      <c r="M48" t="n">
+        <v>771.7453</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4.3814</v>
+      </c>
+      <c r="O48" t="n">
+        <v>763.8223</v>
+      </c>
+      <c r="P48" t="n">
+        <v>3.5416</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>757.6672</v>
+      </c>
+      <c r="R48" t="n">
+        <v>9.6967</v>
+      </c>
+      <c r="S48" t="n">
+        <v>765.3774</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.9865</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>068_d1_jpg.rf.dccd7a7a1610957846e542d412bd78a8.jpg</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>21</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>600.6671</v>
+      </c>
+      <c r="E49" t="n">
+        <v>594.8909</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.9287</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-5.7762</v>
+      </c>
+      <c r="H49" t="n">
+        <v>5.7762</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9616</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>594.9283</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5.7388</v>
+      </c>
+      <c r="M49" t="n">
+        <v>592.9417</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7.7254</v>
+      </c>
+      <c r="O49" t="n">
+        <v>595.3138</v>
+      </c>
+      <c r="P49" t="n">
+        <v>5.3533</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>593.4226</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7.2445</v>
+      </c>
+      <c r="S49" t="n">
+        <v>597.8479</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.8192</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>016_d2_jpg.rf.d69ea271fc8ead7e00a19c4bff62665c.jpg</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>31</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1128.7699</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1126.5872</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7.6448</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-2.1827</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5.5339</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4903</v>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1130.2846</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.5147</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1135.5847</v>
+      </c>
+      <c r="N50" t="n">
+        <v>6.8148</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1115.7497</v>
+      </c>
+      <c r="P50" t="n">
+        <v>13.0202</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1122.4987</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6.2712</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1128.8183</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.0484</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>058_d0_jpg.rf.ab8df462eb38a7cfd65cff39b2992cdb.jpg</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>11</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>611.894</v>
+      </c>
+      <c r="E51" t="n">
+        <v>607.8134</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.7869</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-4.0806</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5.5137</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9011</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>600.8278</v>
+      </c>
+      <c r="L51" t="n">
+        <v>11.0662</v>
+      </c>
+      <c r="M51" t="n">
+        <v>613.1034</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.2094</v>
+      </c>
+      <c r="O51" t="n">
+        <v>614.2674</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.3734</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>600.2146</v>
+      </c>
+      <c r="R51" t="n">
+        <v>11.6794</v>
+      </c>
+      <c r="S51" t="n">
+        <v>610.6539</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.2401</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>018_d1_jpg.rf.4cb760e4db18ad5514645a6d9ee54a47.jpg</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>22</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>666.4124</v>
+      </c>
+      <c r="E52" t="n">
+        <v>671.8402</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.7885</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.4278</v>
+      </c>
+      <c r="H52" t="n">
+        <v>5.4278</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>668.6083</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.1959</v>
+      </c>
+      <c r="M52" t="n">
+        <v>671.2369</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.8245</v>
+      </c>
+      <c r="O52" t="n">
+        <v>674.8356</v>
+      </c>
+      <c r="P52" t="n">
+        <v>8.4232</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>667.9428</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.5304</v>
+      </c>
+      <c r="S52" t="n">
+        <v>676.5771999999999</v>
+      </c>
+      <c r="T52" t="n">
+        <v>10.1648</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>040_d0_jpg.rf.8f2cbb2d727d030158755add43241d12.jpg</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>21</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>604.0789</v>
+      </c>
+      <c r="E53" t="n">
+        <v>600.6281</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.9782</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-3.4508</v>
+      </c>
+      <c r="H53" t="n">
+        <v>5.3964</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>600.441</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.6379</v>
+      </c>
+      <c r="M53" t="n">
+        <v>608.943</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4.8641</v>
+      </c>
+      <c r="O53" t="n">
+        <v>599.7379</v>
+      </c>
+      <c r="P53" t="n">
+        <v>4.341</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>598.2287</v>
+      </c>
+      <c r="R53" t="n">
+        <v>5.8502</v>
+      </c>
+      <c r="S53" t="n">
+        <v>595.7899</v>
+      </c>
+      <c r="T53" t="n">
+        <v>8.289</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>055_d2_jpg.rf.165029284ddb2793ad8deac65e1c3f91.jpg</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>31</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1145.6292</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1146.0636</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.5585</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="H54" t="n">
+        <v>5.214</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1151.9466</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.3174</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1144.7379</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.8913</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1137.8349</v>
+      </c>
+      <c r="P54" t="n">
+        <v>7.7943</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1142.3658</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3.2634</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1153.4326</v>
+      </c>
+      <c r="T54" t="n">
+        <v>7.8034</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>062_d0_jpg.rf.420ca201dfb51cbc2be18110aeb5765e.jpg</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>11</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>664.4782</v>
+      </c>
+      <c r="E55" t="n">
+        <v>669.5536</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.1724</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5.0754</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5.0754</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7638</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>665.7725</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.2943</v>
+      </c>
+      <c r="M55" t="n">
+        <v>669.5804000000001</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5.1022</v>
+      </c>
+      <c r="O55" t="n">
+        <v>675.1212</v>
+      </c>
+      <c r="P55" t="n">
+        <v>10.643</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>665.2782999999999</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.8001</v>
+      </c>
+      <c r="S55" t="n">
+        <v>672.0158</v>
+      </c>
+      <c r="T55" t="n">
+        <v>7.5376</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>036_d0_jpg.rf.cd77e3ba407312ef40811e53f8234dfc.jpg</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>12</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>605.8842</v>
+      </c>
+      <c r="E56" t="n">
+        <v>605.6479</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.4386</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.2363</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.5092</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7442</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>611.0209</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.1367</v>
+      </c>
+      <c r="M56" t="n">
+        <v>605.9172</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="O56" t="n">
+        <v>611.3967</v>
+      </c>
+      <c r="P56" t="n">
+        <v>5.5125</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>595.539</v>
+      </c>
+      <c r="R56" t="n">
+        <v>10.3452</v>
+      </c>
+      <c r="S56" t="n">
+        <v>604.3656999999999</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.5185</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>005_d1_jpg.rf.93c30592402d913f3267450c16f2d887.jpg</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>22</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>630.2604</v>
+      </c>
+      <c r="E57" t="n">
+        <v>630.7971</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.6849</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.3473</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>632.0873</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.8269</v>
+      </c>
+      <c r="M57" t="n">
+        <v>633.7884</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="O57" t="n">
+        <v>634.2699</v>
+      </c>
+      <c r="P57" t="n">
+        <v>4.0095</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>620.7338999999999</v>
+      </c>
+      <c r="R57" t="n">
+        <v>9.5265</v>
+      </c>
+      <c r="S57" t="n">
+        <v>633.1058</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.8454</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>045_d3_jpg.rf.e7b47a708da0d4954eb6d698fb50fbc2.jpg</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>32</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>589.5762999999999</v>
+      </c>
+      <c r="E58" t="n">
+        <v>585.3613</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.6666</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-4.215</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.215</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7149</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>582.974</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6.6023</v>
+      </c>
+      <c r="M58" t="n">
+        <v>586.6641</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.9122</v>
+      </c>
+      <c r="O58" t="n">
+        <v>586.8553000000001</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.721</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>584.3203999999999</v>
+      </c>
+      <c r="R58" t="n">
+        <v>5.2559</v>
+      </c>
+      <c r="S58" t="n">
+        <v>585.9926</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3.5837</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>015_d2_jpg.rf.dae752b5463a5088dc2770f784a243e6.jpg</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>31</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>624.3746</v>
+      </c>
+      <c r="E59" t="n">
+        <v>620.4706</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.4222</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-3.904</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4.0478</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6483</v>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>617.0688</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7.3058</v>
+      </c>
+      <c r="M59" t="n">
+        <v>623.5114</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="O59" t="n">
+        <v>618.8626</v>
+      </c>
+      <c r="P59" t="n">
+        <v>5.512</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>618.176</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6.1986</v>
+      </c>
+      <c r="S59" t="n">
+        <v>624.7341</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.3595</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>052_d1_jpg.rf.3b6940e484968d5a668f3c1f9ae214aa.jpg</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>21</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1370.8864</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1374.7667</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.0882</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.8803</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.8803</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1373.3529</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2.4665</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1373.6673</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.7809</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1377.5478</v>
+      </c>
+      <c r="P60" t="n">
+        <v>6.6614</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1370.9471</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1378.3186</v>
+      </c>
+      <c r="T60" t="n">
+        <v>7.4322</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>001_d1_jpg.rf.55c174a77b98ec1352828ebfa5b9ab51.jpg</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>22</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>409.6467</v>
+      </c>
+      <c r="E61" t="n">
+        <v>407.333</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.7371</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-2.3137</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.7559</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9169</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>403.607</v>
+      </c>
+      <c r="L61" t="n">
+        <v>6.0397</v>
+      </c>
+      <c r="M61" t="n">
+        <v>413.2522</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.6055</v>
+      </c>
+      <c r="O61" t="n">
+        <v>405.8478</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.7989</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>405.481</v>
+      </c>
+      <c r="R61" t="n">
+        <v>4.1657</v>
+      </c>
+      <c r="S61" t="n">
+        <v>408.4772</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.1695</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>046_d1_jpg.rf.ec359b9c3be4b77858006f1894a4fe89.jpg</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>41</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>656.3744</v>
+      </c>
+      <c r="E62" t="n">
+        <v>660.0335</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.4722</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3.6591</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.6591</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>657.0577</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.6833</v>
+      </c>
+      <c r="M62" t="n">
+        <v>658.2269</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1.8525</v>
+      </c>
+      <c r="O62" t="n">
+        <v>663.2175</v>
+      </c>
+      <c r="P62" t="n">
+        <v>6.8431</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>660.1572</v>
+      </c>
+      <c r="R62" t="n">
+        <v>3.7828</v>
+      </c>
+      <c r="S62" t="n">
+        <v>661.5083</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5.1339</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>004_d3_jpg.rf.0908e2acaf0d93383f9ba4d0804e8011.jpg</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>31</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>584.4959</v>
+      </c>
+      <c r="E63" t="n">
+        <v>581.4564</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.0144</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-3.0395</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.0395</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>579.4253</v>
+      </c>
+      <c r="L63" t="n">
+        <v>5.0706</v>
+      </c>
+      <c r="M63" t="n">
+        <v>583.9551</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="O63" t="n">
+        <v>579.8608</v>
+      </c>
+      <c r="P63" t="n">
+        <v>4.6351</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>580.8625</v>
+      </c>
+      <c r="R63" t="n">
+        <v>3.6334</v>
+      </c>
+      <c r="S63" t="n">
+        <v>583.1781</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1.3178</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>067_d0_jpg.rf.5e98d5946a7670ae9374f063be3378c8.jpg</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>11</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>425.8765</v>
+      </c>
+      <c r="E64" t="n">
+        <v>423.5036</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3.2998</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-2.3729</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2.9916</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>421.8187</v>
+      </c>
+      <c r="L64" t="n">
+        <v>4.0578</v>
+      </c>
+      <c r="M64" t="n">
+        <v>425.1569</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="O64" t="n">
+        <v>424.3037</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.5728</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>418.8154</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7.0611</v>
+      </c>
+      <c r="S64" t="n">
+        <v>427.4232</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1.5467</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>044_d2_jpg.rf.da81051630fbd29d52f53bff91f9d894.jpg</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>31</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>341.5896</v>
+      </c>
+      <c r="E65" t="n">
+        <v>343.8207</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.8453</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2.2311</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2.4951</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.7304</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" t="n">
+        <v>340.9294</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.6602</v>
+      </c>
+      <c r="M65" t="n">
+        <v>344.0709</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.4813</v>
+      </c>
+      <c r="O65" t="n">
+        <v>346.0848</v>
+      </c>
+      <c r="P65" t="n">
+        <v>4.4952</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>343.9922</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.4026</v>
+      </c>
+      <c r="S65" t="n">
+        <v>344.026</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.4364</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>029_d1_jpg.rf.60d86604165d1ad5ec3e55f3d4a92ed0.jpg</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>11</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>356.6506</v>
+      </c>
+      <c r="E66" t="n">
+        <v>355.1806</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.0118</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>353.7313</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2.9193</v>
+      </c>
+      <c r="M66" t="n">
+        <v>358.005</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1.3544</v>
+      </c>
+      <c r="O66" t="n">
+        <v>356.1425</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.5081</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>354.3105</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2.3401</v>
+      </c>
+      <c r="S66" t="n">
+        <v>353.7135</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.9371</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>014_d2_jpg.rf.a14a36104d29927ab54f862a9837d584.jpg</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>31</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>587.86</v>
+      </c>
+      <c r="E67" t="n">
+        <v>586.873</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-0.987</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.8379</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>583.643</v>
+      </c>
+      <c r="L67" t="n">
+        <v>4.217</v>
+      </c>
+      <c r="M67" t="n">
+        <v>589.5551</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1.6951</v>
+      </c>
+      <c r="O67" t="n">
+        <v>588.292</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>585.0598</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2.8002</v>
+      </c>
+      <c r="S67" t="n">
+        <v>587.8149</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.0451</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>010_d1_jpg.rf.9c2ea6a8287eca71401d1cb4a5b4c75c.jpg</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>41</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>319.1327</v>
+      </c>
+      <c r="E68" t="n">
+        <v>319.5957</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.3485</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.0968</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>317.9503</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.1824</v>
+      </c>
+      <c r="M68" t="n">
+        <v>318.7306</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="O68" t="n">
+        <v>321.4869</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.3542</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>319.7487</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="S68" t="n">
+        <v>320.0622</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.9295</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>train_seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>牙弓</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>空間</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>剔除碎塊</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>有效張數</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>長度MAE px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>中位數絕對誤差 px</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>平均相對誤差%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>長度偏差(bias) px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>誤差標準差 px</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>最大絕對誤差 px</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>67</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.217</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.278</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-7.561</v>
+      </c>
+      <c r="K2" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="L2" t="n">
+        <v>56.926</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>67</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.774</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-4.427</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.670999999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>40.346</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>53</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14.025</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9.308999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-8.675000000000001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>56.926</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.948</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.973</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-4.979</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="L5" t="n">
+        <v>40.346</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.337</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-3.344</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>19.828</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.329</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2.335</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11.064</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.293</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10.556</v>
+      </c>
+      <c r="L8" t="n">
+        <v>35.964</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.994</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.504</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.835000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.327</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.739</v>
+      </c>
+      <c r="L10" t="n">
+        <v>35.964</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>53</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.842</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.463</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.502</v>
+      </c>
+      <c r="L11" t="n">
+        <v>24.504</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.924</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.044</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.076</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.593</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>67</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11.845</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.559</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-4.234</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15.782</v>
+      </c>
+      <c r="L14" t="n">
+        <v>61.643</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-2.546</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.884</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.233</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>53</v>
+      </c>
+      <c r="G16" t="n">
+        <v>13.323</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.423</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="K16" t="n">
+        <v>17.296</v>
+      </c>
+      <c r="L16" t="n">
+        <v>61.643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.606999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-3.216</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10.769</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.233</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.332</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.181</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.431</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13.02</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.105</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.828</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8.864000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.634</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.492000000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-12.279</v>
+      </c>
+      <c r="K20" t="n">
+        <v>15.415</v>
+      </c>
+      <c r="L20" t="n">
+        <v>64.67100000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.182</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-7.733</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9.762</v>
+      </c>
+      <c r="L21" t="n">
+        <v>39.405</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>53</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10.345</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-14.585</v>
+      </c>
+      <c r="K22" t="n">
+        <v>16.431</v>
+      </c>
+      <c r="L22" t="n">
+        <v>64.67100000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>53</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10.352</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.844</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-9.234999999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="L23" t="n">
+        <v>39.405</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.128</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.751</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.759</v>
+      </c>
+      <c r="L24" t="n">
+        <v>11.467</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.355</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.048</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.361</v>
+      </c>
+      <c r="L25" t="n">
+        <v>8.564</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>67</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10.368</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.233</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-4.472</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.473</v>
+      </c>
+      <c r="L26" t="n">
+        <v>38.161</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>67</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.474</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.385</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.946</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>53</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11.679</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.289</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-6.052</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14.163</v>
+      </c>
+      <c r="L28" t="n">
+        <v>38.161</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>上顎</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>53</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.399</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.642</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-3.575</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.852</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.946</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>原圖</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.403</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.656</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8.397</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.588</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>下顎</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>letterbox</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>mask幾何</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.971</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.901</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.947</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9.907999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
